--- a/requirements-01.xlsx
+++ b/requirements-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fdmxf\Documents\GitHub\junior-soccer-assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050402C9-AC24-4D31-874F-F2602673773F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B74A344-57AE-4413-88FA-47425C387F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13515" xr2:uid="{FDA6C186-3EFB-420E-A56A-AFCC206DDE42}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>نام قطعه</t>
   </si>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>مجموع هزینه</t>
+  </si>
+  <si>
+    <t>آینه</t>
+  </si>
+  <si>
+    <t>پرینتر سه بعدی</t>
   </si>
 </sst>
 </file>
@@ -705,11 +711,17 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="E8" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E9" s="5">
         <v>0</v>
       </c>
